--- a/data/trans_dic/P2A_ner_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P2A_ner_R-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con problemas de nervios, depresión o trastorno mental</t>
+          <t>Hogares con personas con problemas de nervios, depresión o trastorno mental (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +639,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -716,69 +717,69 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,41; 12,35</t>
+          <t>1,4; 13,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,35</t>
+          <t>0,0; 13,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,05; 19,7</t>
+          <t>5,23; 18,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,3</t>
+          <t>0,0; 5,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,73; 16,86</t>
+          <t>3,83; 16,04</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,28</t>
+          <t>0,0; 10,51</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,6; 14,84</t>
+          <t>1,57; 15,74</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,86</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,42; 11,99</t>
+          <t>3,31; 11,8</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,81</t>
+          <t>0,0; 8,71</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,43; 13,18</t>
+          <t>4,13; 13,16</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,37</t>
+          <t>0,0; 2,39</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,69 +857,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,53</t>
+          <t>0,0; 5,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,14; 10,48</t>
+          <t>1,12; 9,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,35; 10,78</t>
+          <t>1,85; 11,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,33; 8,32</t>
+          <t>1,54; 8,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,94</t>
+          <t>0,0; 6,51</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 2,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,89; 10,21</t>
+          <t>2,36; 10,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,89; 7,48</t>
+          <t>2,03; 7,88</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,73</t>
+          <t>0,48; 4,34</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,55; 4,76</t>
+          <t>0,55; 4,55</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,81; 8,73</t>
+          <t>2,73; 8,74</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,21; 6,83</t>
+          <t>2,23; 6,75</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,31</t>
+          <t>0,0; 5,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,62</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,51</t>
+          <t>0,0; 5,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,33</t>
+          <t>0,0; 8,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,6</t>
+          <t>0,0; 5,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,2</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,11; 11,95</t>
+          <t>1,7; 10,95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,13; 11,12</t>
+          <t>2,15; 10,84</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,47</t>
+          <t>0,0; 3,31</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,21</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,23; 7,37</t>
+          <t>1,28; 7,26</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,82; 7,2</t>
+          <t>1,54; 7,45</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,48</t>
+          <t>0,0; 6,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,6; 13,2</t>
+          <t>1,54; 13,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,7; 15,05</t>
+          <t>2,71; 15,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,47; 7,69</t>
+          <t>0,25; 6,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,16</t>
+          <t>0,0; 7,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,2; 10,79</t>
+          <t>1,17; 11,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,8; 22,65</t>
+          <t>5,2; 22,77</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0; 2,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,65</t>
+          <t>0,47; 4,41</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,39; 9,5</t>
+          <t>2,58; 10,31</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,57; 16,75</t>
+          <t>5,44; 16,23</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,24; 3,64</t>
+          <t>0,22; 3,31</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,18</t>
+          <t>0,0; 30,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,7; 31,8</t>
+          <t>3,67; 33,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,14; 20,25</t>
+          <t>2,12; 19,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,32</t>
+          <t>0,0; 7,7</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,19</t>
+          <t>0,0; 14,23</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,68; 14,88</t>
+          <t>1,67; 15,5</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,36</t>
+          <t>0,0; 7,48</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,27</t>
+          <t>0,0; 15,15</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,11; 16,13</t>
+          <t>1,68; 15,3</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,96; 13,85</t>
+          <t>3,01; 13,43</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,63</t>
+          <t>0,0; 4,82</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1416,69 +1417,69 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,13</t>
+          <t>0,0; 11,17</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,17</t>
+          <t>0,0; 15,93</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,1; 11,71</t>
+          <t>1,13; 10,63</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,16</t>
+          <t>0,0; 7,11</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,43</t>
+          <t>0,0; 14,56</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,92; 9,17</t>
+          <t>0,88; 7,91</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,86</t>
+          <t>0,0; 4,5</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,61</t>
+          <t>0,0; 5,37</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,28; 11,84</t>
+          <t>1,23; 11,71</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,51; 7,23</t>
+          <t>1,61; 7,21</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,6</t>
+          <t>0,0; 3,85</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,78</t>
+          <t>0,0; 3,79</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,23; 7,73</t>
+          <t>1,2; 7,62</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,93; 9,73</t>
+          <t>3,15; 9,81</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,65; 6,61</t>
+          <t>0,61; 6,36</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,53; 4,58</t>
+          <t>0,53; 4,68</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,57; 4,75</t>
+          <t>0,57; 4,8</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,47; 13,44</t>
+          <t>4,52; 13,21</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,65; 3,98</t>
+          <t>0,89; 3,75</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,56; 3,12</t>
+          <t>0,56; 3,13</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,2; 4,85</t>
+          <t>1,16; 4,88</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,55; 10,51</t>
+          <t>4,66; 10,11</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,41; 8,16</t>
+          <t>1,42; 8,47</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,17; 6,92</t>
+          <t>1,14; 6,46</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,25; 7,89</t>
+          <t>1,99; 7,88</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8,93; 19,35</t>
+          <t>8,75; 19,79</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,19; 6,82</t>
+          <t>1,01; 7,19</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,69</t>
+          <t>0,0; 3,27</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,7; 6,47</t>
+          <t>1,44; 7,08</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>9,04; 18,75</t>
+          <t>8,6; 18,64</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,93; 6,2</t>
+          <t>1,84; 6,11</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,84; 4,03</t>
+          <t>0,84; 4,07</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2,26; 6,01</t>
+          <t>2,37; 5,97</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>10,01; 17,02</t>
+          <t>10,19; 16,79</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,38</t>
+          <t>1,35; 3,44</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,93; 4,54</t>
+          <t>1,89; 4,58</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,68; 6,75</t>
+          <t>3,57; 6,71</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,05; 7,06</t>
+          <t>4,05; 7,01</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,76; 4,11</t>
+          <t>1,7; 4,04</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,39</t>
+          <t>0,75; 2,43</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,51; 6,42</t>
+          <t>3,42; 6,43</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,33; 7,53</t>
+          <t>4,34; 7,31</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,77; 3,31</t>
+          <t>1,74; 3,33</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1,52; 3,05</t>
+          <t>1,44; 2,96</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3,95; 6,05</t>
+          <t>3,9; 6,01</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>4,6; 6,74</t>
+          <t>4,58; 6,69</t>
         </is>
       </c>
     </row>
@@ -1920,4 +1921,2040 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Hogares con personas con problemas de nervios, depresión o trastorno mental (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2465</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>736</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4693</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>4252</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>839</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>3079</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>6716</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>1575</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>7771</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>668; 6423</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3356</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2372; 8374</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3661</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1959; 8207</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4002</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>816; 8184</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>3278; 11671</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5528</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>4021; 12815</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3644</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1245</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1911</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3856</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>5241</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1284</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>4160</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>5057</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>2529</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>1911</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>8016</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>10298</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3791</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>611; 4930</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1309; 8274</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1960; 10938</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4229</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>1887; 8462</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>2592; 10053</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>633; 5765</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>620; 5157</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>4112; 13176</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>5696; 17235</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>678</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1191</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>635</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>3581</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>3584</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>1313</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>4417</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>4775</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3782</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3352</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4776</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3808</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>1126; 7249</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>1444; 7280</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4394</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>1586; 9029</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>1933; 9348</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>857</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3059</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>3290</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1454</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1499</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2511</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>5756</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>2356</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>5570</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>9046</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>1454</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4158</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>764; 6624</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>1222; 7065</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>173; 4902</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5255</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>649; 6201</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>2479; 10848</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>659; 6155</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>2716; 10845</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>5048; 15054</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>319; 4908</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>622</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2288</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2711</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>573</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>622</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>2935</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>4714</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>1174</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2895</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>662; 5978</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>685; 6230</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2659</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3506</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>595; 5506</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3044</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3173</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>716; 6530</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>2042; 9115</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3623</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1232</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1429</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>1815</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1232</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>1408</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>1680</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>1232</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>1232</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>2838</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>3496</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4975</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4345</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>521; 4909</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3719</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4565</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>493; 4445</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4450</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>0; 5055</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>720; 6869</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>1646; 7377</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>1406</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>1348</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>3887</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>7089</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>2703</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>2034</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>2114</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>12408</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>4110</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>3382</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>6001</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>19497</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4261</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4421</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>1401; 8901</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>3925; 12215</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>681; 7049</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>644; 5694</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>680; 5720</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>7045; 20603</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>1971; 8307</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>1343; 7470</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>2729; 11515</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>13078; 28359</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>3727</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>3610</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>5586</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>17597</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>2844</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>1369</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>4987</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>20524</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>6571</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>4979</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>10573</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>38121</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>1282; 7640</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>1319; 7458</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>2581; 10211</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>11521; 26044</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>972; 6940</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>0; 4266</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>2002; 9855</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>13479; 29234</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>3440; 11409</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>2056; 10025</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>6368; 16046</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>29397; 48416</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>11000</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>14185</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>26289</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>36062</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>14449</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>7400</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>27087</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>43855</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>25448</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>21585</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>53375</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>79916</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>6795; 17334</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>9022; 21847</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>18735; 35273</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>26948; 46707</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>8985; 21348</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>4017; 13079</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>19518; 36715</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>33070; 55711</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>17985; 34398</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>14645; 30019</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>42709; 65880</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>65472; 95484</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/P2A_ner_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P2A_ner_R-Provincia-trans_dic.xlsx
@@ -717,37 +717,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,4; 13,46</t>
+          <t>1,38; 11,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,24</t>
+          <t>0,0; 14,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,23; 18,45</t>
+          <t>4,93; 19,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,0</t>
+          <t>0,0; 5,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,83; 16,04</t>
+          <t>3,14; 16,91</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,51</t>
+          <t>0,0; 10,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,57; 15,74</t>
+          <t>1,56; 13,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -757,22 +757,22 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,31; 11,8</t>
+          <t>3,24; 12,05</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,71</t>
+          <t>0,0; 7,63</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,13; 13,16</t>
+          <t>4,3; 13,2</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,39</t>
+          <t>0,0; 2,31</t>
         </is>
       </c>
     </row>
@@ -857,27 +857,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,58</t>
+          <t>0,0; 6,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,12; 9,06</t>
+          <t>1,14; 9,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,85; 11,7</t>
+          <t>1,87; 11,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,54; 8,57</t>
+          <t>1,24; 8,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,51</t>
+          <t>0,0; 6,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -887,32 +887,32 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,36; 10,58</t>
+          <t>2,35; 10,31</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,03; 7,88</t>
+          <t>1,82; 7,21</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,34</t>
+          <t>0,48; 4,67</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,55; 4,55</t>
+          <t>0,55; 4,19</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,73; 8,74</t>
+          <t>2,92; 9,23</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,23; 6,75</t>
+          <t>2,07; 6,4</t>
         </is>
       </c>
     </row>
@@ -997,7 +997,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,85</t>
+          <t>0,0; 5,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,77</t>
+          <t>0,0; 7,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,2</t>
+          <t>0,0; 6,68</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,61</t>
+          <t>0,0; 4,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1027,17 +1027,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,7; 10,95</t>
+          <t>2,12; 11,95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,15; 10,84</t>
+          <t>2,21; 12,29</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,31</t>
+          <t>0,0; 4,18</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1047,12 +1047,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,28; 7,26</t>
+          <t>1,24; 7,17</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,54; 7,45</t>
+          <t>1,64; 7,36</t>
         </is>
       </c>
     </row>
@@ -1137,37 +1137,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,3</t>
+          <t>0,0; 6,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,54; 13,33</t>
+          <t>1,64; 14,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,71; 15,66</t>
+          <t>2,75; 15,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,25; 6,99</t>
+          <t>0,24; 7,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,15</t>
+          <t>0,0; 6,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,17; 11,18</t>
+          <t>1,2; 10,96</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,2; 22,77</t>
+          <t>4,97; 22,44</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1177,22 +1177,22 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,41</t>
+          <t>0,47; 5,21</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,58; 10,31</t>
+          <t>2,54; 9,84</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,44; 16,23</t>
+          <t>5,24; 15,66</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,22; 3,31</t>
+          <t>0,11; 3,47</t>
         </is>
       </c>
     </row>
@@ -1277,22 +1277,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,34</t>
+          <t>0,0; 34,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,67; 33,13</t>
+          <t>3,67; 34,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,12; 19,24</t>
+          <t>2,07; 19,01</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,7</t>
+          <t>0,0; 8,27</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1302,37 +1302,37 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,23</t>
+          <t>0,0; 15,33</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,67; 15,5</t>
+          <t>1,68; 15,27</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,48</t>
+          <t>0,0; 6,85</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,15</t>
+          <t>0,0; 12,22</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,68; 15,3</t>
+          <t>1,69; 15,96</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,01; 13,43</t>
+          <t>2,95; 13,75</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,82</t>
+          <t>0,0; 5,65</t>
         </is>
       </c>
     </row>
@@ -1422,22 +1422,22 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,17</t>
+          <t>0,0; 8,95</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,93</t>
+          <t>0,0; 16,26</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,13; 10,63</t>
+          <t>1,1; 10,63</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,11</t>
+          <t>0,0; 8,34</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1447,32 +1447,32 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,56</t>
+          <t>0,0; 15,92</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,88; 7,91</t>
+          <t>0,91; 8,61</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,5</t>
+          <t>0,0; 3,86</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,37</t>
+          <t>0,0; 4,54</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,23; 11,71</t>
+          <t>1,2; 11,74</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,61; 7,21</t>
+          <t>1,56; 6,72</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,85</t>
+          <t>0,0; 4,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,79</t>
+          <t>0,0; 3,9</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,2; 7,62</t>
+          <t>1,22; 7,93</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,15; 9,81</t>
+          <t>2,74; 9,9</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,61; 6,36</t>
+          <t>0,59; 6,03</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,53; 4,68</t>
+          <t>0,53; 4,48</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,57; 4,8</t>
+          <t>0,57; 4,75</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,52; 13,21</t>
+          <t>4,26; 13,45</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,89; 3,75</t>
+          <t>0,63; 3,76</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,56; 3,13</t>
+          <t>0,55; 3,15</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,16; 4,88</t>
+          <t>1,36; 5,53</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,66; 10,11</t>
+          <t>4,47; 10,09</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,42; 8,47</t>
+          <t>1,38; 8,35</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,14; 6,46</t>
+          <t>1,19; 6,7</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,99; 7,88</t>
+          <t>1,96; 7,87</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8,75; 19,79</t>
+          <t>8,91; 19,08</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,01; 7,19</t>
+          <t>1,02; 6,5</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,27</t>
+          <t>0,0; 4,34</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,44; 7,08</t>
+          <t>1,44; 6,59</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>8,6; 18,64</t>
+          <t>8,72; 17,98</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,84; 6,11</t>
+          <t>1,89; 6,23</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,84; 4,07</t>
+          <t>0,86; 3,9</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2,37; 5,97</t>
+          <t>2,38; 6,27</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>10,19; 16,79</t>
+          <t>10,03; 17,02</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,44</t>
+          <t>1,25; 3,42</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,89; 4,58</t>
+          <t>1,84; 4,62</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,57; 6,71</t>
+          <t>3,72; 6,79</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,05; 7,01</t>
+          <t>4,17; 7,06</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,7; 4,04</t>
+          <t>1,74; 3,9</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,43</t>
+          <t>0,73; 2,36</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,42; 6,43</t>
+          <t>3,5; 6,52</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,34; 7,31</t>
+          <t>4,41; 7,39</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,74; 3,33</t>
+          <t>1,76; 3,39</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1,44; 2,96</t>
+          <t>1,43; 2,96</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3,9; 6,01</t>
+          <t>3,79; 5,99</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>4,58; 6,69</t>
+          <t>4,58; 6,72</t>
         </is>
       </c>
     </row>
@@ -2209,37 +2209,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>668; 6423</t>
+          <t>659; 5672</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3356</t>
+          <t>0; 3631</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2372; 8374</t>
+          <t>2239; 8884</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3661</t>
+          <t>0; 3706</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1959; 8207</t>
+          <t>1609; 8653</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 4002</t>
+          <t>0; 4159</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>816; 8184</t>
+          <t>809; 7247</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -2249,22 +2249,22 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3278; 11671</t>
+          <t>3201; 11911</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 5528</t>
+          <t>0; 4838</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4021; 12815</t>
+          <t>4190; 12850</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 3644</t>
+          <t>0; 3523</t>
         </is>
       </c>
     </row>
@@ -2417,27 +2417,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3791</t>
+          <t>0; 4418</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>611; 4930</t>
+          <t>618; 5213</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1309; 8274</t>
+          <t>1324; 7993</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1960; 10938</t>
+          <t>1580; 10334</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4229</t>
+          <t>0; 3981</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -2447,32 +2447,32 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1887; 8462</t>
+          <t>1883; 8248</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2592; 10053</t>
+          <t>2322; 9195</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>633; 5765</t>
+          <t>642; 6205</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>620; 5157</t>
+          <t>619; 4749</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4112; 13176</t>
+          <t>4396; 13914</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5696; 17235</t>
+          <t>5276; 16344</t>
         </is>
       </c>
     </row>
@@ -2625,7 +2625,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3782</t>
+          <t>0; 3419</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -2635,17 +2635,17 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3352</t>
+          <t>0; 4321</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4776</t>
+          <t>0; 3890</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3808</t>
+          <t>0; 3185</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -2655,17 +2655,17 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1126; 7249</t>
+          <t>1405; 7907</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1444; 7280</t>
+          <t>1485; 8257</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 4394</t>
+          <t>0; 5543</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -2675,12 +2675,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1586; 9029</t>
+          <t>1544; 8918</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1933; 9348</t>
+          <t>2053; 9226</t>
         </is>
       </c>
     </row>
@@ -2833,37 +2833,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4158</t>
+          <t>0; 4239</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>764; 6624</t>
+          <t>814; 7252</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1222; 7065</t>
+          <t>1241; 7051</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>173; 4902</t>
+          <t>170; 4930</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 5255</t>
+          <t>0; 4771</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>649; 6201</t>
+          <t>663; 6078</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2479; 10848</t>
+          <t>2367; 10694</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2873,22 +2873,22 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>659; 6155</t>
+          <t>657; 7274</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2716; 10845</t>
+          <t>2676; 10344</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5048; 15054</t>
+          <t>4862; 14531</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>319; 4908</t>
+          <t>166; 5140</t>
         </is>
       </c>
     </row>
@@ -3041,22 +3041,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 2895</t>
+          <t>0; 3253</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>662; 5978</t>
+          <t>662; 6226</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>685; 6230</t>
+          <t>669; 6154</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 2659</t>
+          <t>0; 2855</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -3066,37 +3066,37 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 3506</t>
+          <t>0; 3775</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>595; 5506</t>
+          <t>596; 5423</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 3044</t>
+          <t>0; 2791</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 3173</t>
+          <t>0; 2558</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>716; 6530</t>
+          <t>721; 6809</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2042; 9115</t>
+          <t>2005; 9335</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 3623</t>
+          <t>0; 4254</t>
         </is>
       </c>
     </row>
@@ -3254,22 +3254,22 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 4975</t>
+          <t>0; 3987</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 4345</t>
+          <t>0; 4437</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>521; 4909</t>
+          <t>507; 4909</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 3719</t>
+          <t>0; 4357</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -3279,32 +3279,32 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 4565</t>
+          <t>0; 4993</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>493; 4445</t>
+          <t>511; 4840</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 4450</t>
+          <t>0; 3817</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 5055</t>
+          <t>0; 4266</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>720; 6869</t>
+          <t>706; 6882</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1646; 7377</t>
+          <t>1599; 6880</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 4261</t>
+          <t>0; 4926</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 4421</t>
+          <t>0; 4550</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1401; 8901</t>
+          <t>1426; 9263</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3925; 12215</t>
+          <t>3407; 12322</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>681; 7049</t>
+          <t>656; 6683</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>644; 5694</t>
+          <t>645; 5457</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>680; 5720</t>
+          <t>680; 5661</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>7045; 20603</t>
+          <t>6653; 20987</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1971; 8307</t>
+          <t>1398; 8329</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1343; 7470</t>
+          <t>1319; 7521</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2729; 11515</t>
+          <t>3198; 13039</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>13078; 28359</t>
+          <t>12547; 28303</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1282; 7640</t>
+          <t>1241; 7531</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1319; 7458</t>
+          <t>1376; 7736</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2581; 10211</t>
+          <t>2542; 10203</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>11521; 26044</t>
+          <t>11725; 25114</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>972; 6940</t>
+          <t>982; 6278</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0; 4266</t>
+          <t>0; 5658</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2002; 9855</t>
+          <t>2011; 9171</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>13479; 29234</t>
+          <t>13675; 28191</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3440; 11409</t>
+          <t>3536; 11631</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2056; 10025</t>
+          <t>2115; 9584</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>6368; 16046</t>
+          <t>6400; 16854</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>29397; 48416</t>
+          <t>28933; 49081</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>6795; 17334</t>
+          <t>6303; 17237</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>9022; 21847</t>
+          <t>8788; 22044</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>18735; 35273</t>
+          <t>19551; 35676</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>26948; 46707</t>
+          <t>27771; 47056</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>8985; 21348</t>
+          <t>9182; 20637</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4017; 13079</t>
+          <t>3953; 12722</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>19518; 36715</t>
+          <t>19984; 37235</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>33070; 55711</t>
+          <t>33568; 56348</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>17985; 34398</t>
+          <t>18112; 34993</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>14645; 30019</t>
+          <t>14501; 30036</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>42709; 65880</t>
+          <t>41585; 65626</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>65472; 95484</t>
+          <t>65345; 95924</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_ner_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P2A_ner_R-Provincia-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>8,31%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2,2%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5,92%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>5,17%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>2,9%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>10,34%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,5%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>8,31%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,2%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>5,92%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,86%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,38; 11,89</t>
+          <t>3,73; 16,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,32</t>
+          <t>0,0; 12,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,93; 19,57</t>
+          <t>1,6; 14,84</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,14; 16,91</t>
+          <t>1,41; 12,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,92</t>
+          <t>0,0; 12,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,56; 13,94</t>
+          <t>5,05; 19,7</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 6,35</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,24; 12,05</t>
+          <t>3,42; 11,99</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,63</t>
+          <t>0,0; 7,81</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,3; 13,2</t>
+          <t>4,43; 13,18</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,31</t>
+          <t>0,0; 2,89</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1,98%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>5,2%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>3,84%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>1,83%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>3,51%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>5,45%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4,11%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1,98%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>5,2%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,51</t>
+          <t>0,0; 6,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,14; 9,59</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,87; 11,31</t>
+          <t>1,89; 10,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,24; 8,1</t>
+          <t>1,81; 7,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,13</t>
+          <t>0,0; 5,53</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,14; 10,48</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,35; 10,31</t>
+          <t>2,35; 10,78</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,82; 7,21</t>
+          <t>2,1; 9,48</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,67</t>
+          <t>0,48; 4,73</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,55; 4,19</t>
+          <t>0,55; 4,76</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,92; 9,23</t>
+          <t>2,81; 8,73</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,07; 6,4</t>
+          <t>2,55; 7,4</t>
         </is>
       </c>
     </row>
@@ -929,54 +929,54 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5,41%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>5,46%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>1,05%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>1,44%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2,04%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1,98%</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0,99%</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>5,41%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>5,34%</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
           <t>3,55%</t>
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -997,7 +997,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,28</t>
+          <t>0,0; 5,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,44</t>
+          <t>2,11; 11,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,68</t>
+          <t>2,19; 11,52</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,69</t>
+          <t>0,0; 6,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1027,17 +1027,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,12; 11,95</t>
+          <t>0,0; 6,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,21; 12,29</t>
+          <t>0,0; 7,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,18</t>
+          <t>0,0; 3,47</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1047,12 +1047,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,24; 7,17</t>
+          <t>1,23; 7,37</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,64; 7,36</t>
+          <t>1,76; 7,17</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2,04%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4,53%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>12,08%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>1,3%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>6,16%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>7,29%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2,07%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2,04%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4,53%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>12,08%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,42</t>
+          <t>0,0; 7,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,64; 14,6</t>
+          <t>1,2; 10,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,75; 15,63</t>
+          <t>4,8; 22,65</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,24; 7,03</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,49</t>
+          <t>0,0; 6,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,2; 10,96</t>
+          <t>1,6; 13,2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,97; 22,44</t>
+          <t>2,7; 15,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,51; 7,99</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,47; 5,21</t>
+          <t>0,48; 4,65</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,54; 9,84</t>
+          <t>2,39; 9,5</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,24; 15,66</t>
+          <t>5,57; 16,75</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,11; 3,47</t>
+          <t>0,25; 4,09</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2,63%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5,64%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>6,52%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>12,68%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>8,37%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2,63%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>5,64%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,1</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,67; 34,51</t>
+          <t>0,0; 12,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,07; 19,01</t>
+          <t>1,68; 14,88</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,27</t>
+          <t>0,0; 7,53</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 29,18</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,33</t>
+          <t>3,7; 31,8</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,68; 15,27</t>
+          <t>2,14; 20,25</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,85</t>
+          <t>0,0; 7,09</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,22</t>
+          <t>0,0; 15,27</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,69; 15,96</t>
+          <t>2,11; 16,13</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,95; 13,75</t>
+          <t>2,96; 13,85</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,65</t>
+          <t>0,0; 5,48</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2,36%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>4,49%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3,43%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>2,77%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>5,24%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>3,93%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>2,36%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>4,49%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -1417,42 +1417,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>0,0; 7,16</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 8,95</t>
-        </is>
-      </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,26</t>
+          <t>0,0; 14,43</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,1; 10,63</t>
+          <t>1,05; 10,17</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 10,13</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,92</t>
+          <t>0,0; 16,17</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,91; 8,61</t>
+          <t>1,16; 11,14</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1462,17 +1462,17 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,54</t>
+          <t>0,0; 4,61</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,2; 11,74</t>
+          <t>1,28; 11,84</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,56; 6,72</t>
+          <t>1,49; 7,63</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2,44%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1,77%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>8,27%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>1,27%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>1,16%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>3,33%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5,69%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2,44%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,77%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,31%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,45</t>
+          <t>0,65; 6,61</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,9</t>
+          <t>0,53; 4,58</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,22; 7,93</t>
+          <t>0,57; 4,75</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,74; 9,9</t>
+          <t>4,57; 13,61</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,59; 6,03</t>
+          <t>0,0; 4,6</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,53; 4,48</t>
+          <t>0,0; 3,78</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,57; 4,75</t>
+          <t>1,23; 7,73</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,26; 13,45</t>
+          <t>3,22; 10,37</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,76</t>
+          <t>0,65; 3,98</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,55; 3,15</t>
+          <t>0,56; 3,12</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,36; 5,53</t>
+          <t>1,2; 4,85</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,47; 10,09</t>
+          <t>4,96; 11,04</t>
         </is>
       </c>
     </row>
@@ -1629,42 +1629,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>2,95%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>1,05%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>3,58%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>12,98%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>4,13%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>3,12%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>4,31%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>13,37%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>2,95%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>3,58%</t>
-        </is>
-      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,02%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,38; 8,35</t>
+          <t>1,19; 6,82</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,19; 6,7</t>
+          <t>0,0; 3,69</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,96; 7,87</t>
+          <t>1,7; 6,47</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8,91; 19,08</t>
+          <t>8,61; 18,76</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,02; 6,5</t>
+          <t>1,41; 8,16</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,34</t>
+          <t>1,17; 6,92</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,44; 6,59</t>
+          <t>2,25; 7,89</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>8,72; 17,98</t>
+          <t>8,62; 19,09</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,89; 6,23</t>
+          <t>1,93; 6,2</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,86; 3,9</t>
+          <t>0,84; 4,03</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2,38; 6,27</t>
+          <t>2,26; 6,01</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>10,03; 17,02</t>
+          <t>9,79; 16,93</t>
         </is>
       </c>
     </row>
@@ -1769,42 +1769,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>2,73%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>4,74%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>6,04%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>2,19%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>2,97%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>5,0%</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>5,41%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>2,73%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>1,37%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>4,74%</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,25; 3,42</t>
+          <t>1,76; 4,11</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,84; 4,62</t>
+          <t>0,67; 2,39</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,72; 6,79</t>
+          <t>3,51; 6,42</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,17; 7,06</t>
+          <t>4,49; 7,97</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,74; 3,9</t>
+          <t>1,37; 3,38</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,36</t>
+          <t>1,93; 4,54</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,5; 6,52</t>
+          <t>3,68; 6,75</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,41; 7,39</t>
+          <t>4,48; 7,64</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,76; 3,39</t>
+          <t>1,77; 3,31</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1,43; 2,96</t>
+          <t>1,52; 3,05</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3,79; 5,99</t>
+          <t>3,95; 6,05</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>4,58; 6,72</t>
+          <t>4,9; 7,21</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1957,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1965,7 +1965,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -2073,42 +2073,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -2141,42 +2141,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>4252</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>839</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3079</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>2465</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>736</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>4693</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1101</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>4252</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>839</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>3079</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>1040</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>659; 5672</t>
+          <t>1908; 8628</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3631</t>
+          <t>0; 4678</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2239; 8884</t>
+          <t>832; 7717</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3706</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1609; 8653</t>
+          <t>674; 5893</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 4159</t>
+          <t>0; 3130</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>809; 7247</t>
+          <t>2293; 8941</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3589</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3201; 11911</t>
+          <t>3378; 11856</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 4838</t>
+          <t>0; 4952</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4190; 12850</t>
+          <t>4316; 12832</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 3523</t>
+          <t>0; 3483</t>
         </is>
       </c>
     </row>
@@ -2286,37 +2286,37 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2349,42 +2349,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1284</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4160</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4450</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>1245</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1911</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>3856</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5241</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1284</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>4160</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5057</t>
+          <t>5221</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>10298</t>
+          <t>9670</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4418</t>
+          <t>0; 4509</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>618; 5213</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1324; 7993</t>
+          <t>1508; 8171</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1580; 10334</t>
+          <t>2102; 8637</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3981</t>
+          <t>0; 3757</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>622; 5701</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1883; 8248</t>
+          <t>1664; 7625</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2322; 9195</t>
+          <t>2133; 9610</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>642; 6205</t>
+          <t>635; 6277</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>619; 4749</t>
+          <t>620; 5389</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4396; 13914</t>
+          <t>4229; 13160</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5276; 16344</t>
+          <t>5550; 16065</t>
         </is>
       </c>
     </row>
@@ -2499,32 +2499,32 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2557,54 +2557,54 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>635</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>3581</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>3242</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>678</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>836</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1191</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>635</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1121</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>1313</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>3581</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>3584</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>1313</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
           <t>4417</t>
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4775</t>
+          <t>4363</t>
         </is>
       </c>
     </row>
@@ -2625,7 +2625,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3419</t>
+          <t>0; 3802</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -2635,17 +2635,17 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4321</t>
+          <t>1395; 7908</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3890</t>
+          <t>1300; 6842</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3185</t>
+          <t>0; 4086</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -2655,17 +2655,17 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1405; 7907</t>
+          <t>0; 3780</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1485; 8257</t>
+          <t>0; 3961</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 5543</t>
+          <t>0; 4604</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -2675,12 +2675,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1544; 8918</t>
+          <t>1534; 9156</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2053; 9226</t>
+          <t>2044; 8308</t>
         </is>
       </c>
     </row>
@@ -2697,42 +2697,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2765,42 +2765,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1499</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2511</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>5756</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>857</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>3059</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>3290</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1454</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1499</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2511</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>5756</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1641</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1454</t>
+          <t>1641</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4239</t>
+          <t>0; 5262</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>814; 7252</t>
+          <t>668; 5986</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1241; 7051</t>
+          <t>2285; 10792</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>170; 4930</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4771</t>
+          <t>0; 4278</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>663; 6078</t>
+          <t>793; 6559</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2367; 10694</t>
+          <t>1219; 6789</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>358; 5658</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>657; 7274</t>
+          <t>668; 6491</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2676; 10344</t>
+          <t>2518; 9992</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4862; 14531</t>
+          <t>5164; 15536</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>166; 5140</t>
+          <t>362; 5847</t>
         </is>
       </c>
     </row>
@@ -2905,37 +2905,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2973,42 +2973,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>571</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>622</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>2288</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>2711</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>573</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>647</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>2003</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>574</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1174</t>
+          <t>1145</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 3253</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>662; 6226</t>
+          <t>0; 3003</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>669; 6154</t>
+          <t>598; 5285</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 2855</t>
+          <t>0; 2979</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2784</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 3775</t>
+          <t>667; 5737</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>596; 5423</t>
+          <t>694; 6555</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 2791</t>
+          <t>0; 2524</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 2558</t>
+          <t>0; 3197</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>721; 6809</t>
+          <t>902; 6885</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2005; 9335</t>
+          <t>2010; 9404</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 4254</t>
+          <t>0; 4117</t>
         </is>
       </c>
     </row>
@@ -3113,37 +3113,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -3181,54 +3181,54 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1232</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1408</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>1681</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>1232</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>1429</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1815</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>1777</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>1232</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1408</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>1680</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>1232</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>1232</t>
-        </is>
-      </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
           <t>2838</t>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>3496</t>
+          <t>3457</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>0; 3740</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>0; 3987</t>
-        </is>
-      </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 4437</t>
+          <t>0; 4526</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>507; 4909</t>
+          <t>515; 4978</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 4357</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4511</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 4993</t>
+          <t>0; 4411</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>511; 4840</t>
+          <t>529; 5098</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 3817</t>
+          <t>0; 3822</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 4266</t>
+          <t>0; 4340</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>706; 6882</t>
+          <t>748; 6941</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1599; 6880</t>
+          <t>1414; 7222</t>
         </is>
       </c>
     </row>
@@ -3321,42 +3321,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3389,42 +3389,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>2703</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>2034</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>2114</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>11694</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>1406</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>1348</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>3887</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>7089</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>2703</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>2034</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>2114</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>12408</t>
+          <t>7594</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>19497</t>
+          <t>19288</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 4926</t>
+          <t>724; 7317</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 4550</t>
+          <t>644; 5581</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1426; 9263</t>
+          <t>683; 5662</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3407; 12322</t>
+          <t>6465; 19242</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>656; 6683</t>
+          <t>0; 5092</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>645; 5457</t>
+          <t>0; 4408</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>680; 5661</t>
+          <t>1438; 9023</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>6653; 20987</t>
+          <t>3942; 12704</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1398; 8329</t>
+          <t>1440; 8824</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1319; 7521</t>
+          <t>1344; 7452</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3198; 13039</t>
+          <t>2829; 11442</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>12547; 28303</t>
+          <t>13097; 29135</t>
         </is>
       </c>
     </row>
@@ -3529,42 +3529,42 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>25</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -3597,42 +3597,42 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>2844</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>1369</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>4987</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>20690</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>3727</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>3610</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>5586</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>17597</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>2844</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>1369</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>4987</t>
-        </is>
-      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>20524</t>
+          <t>18351</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>38121</t>
+          <t>39041</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1241; 7531</t>
+          <t>1151; 6582</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1376; 7736</t>
+          <t>0; 4815</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2542; 10203</t>
+          <t>2373; 9013</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>11725; 25114</t>
+          <t>13728; 29914</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>982; 6278</t>
+          <t>1269; 7357</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0; 5658</t>
+          <t>1356; 7990</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2011; 9171</t>
+          <t>2923; 10236</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>13675; 28191</t>
+          <t>12108; 26824</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3536; 11631</t>
+          <t>3613; 11571</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2115; 9584</t>
+          <t>2066; 9926</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>6400; 16854</t>
+          <t>6064; 16149</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>28933; 49081</t>
+          <t>29374; 50773</t>
         </is>
       </c>
     </row>
@@ -3737,42 +3737,42 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>55</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -3805,42 +3805,42 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>14449</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>7400</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>27087</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>42328</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
           <t>11000</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>14185</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>26289</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>36062</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>14449</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>7400</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>27087</t>
-        </is>
-      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>43855</t>
+          <t>37319</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>79916</t>
+          <t>79646</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>6303; 17237</t>
+          <t>9318; 21718</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>8788; 22044</t>
+          <t>3583; 12897</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>19551; 35676</t>
+          <t>20042; 36656</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>27771; 47056</t>
+          <t>31498; 55840</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>9182; 20637</t>
+          <t>6875; 17028</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3953; 12722</t>
+          <t>9196; 21670</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>19984; 37235</t>
+          <t>19342; 35472</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>33568; 56348</t>
+          <t>28185; 48112</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>18112; 34993</t>
+          <t>18219; 34190</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>14501; 30036</t>
+          <t>15435; 30955</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>41585; 65626</t>
+          <t>43336; 66358</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>65345; 95924</t>
+          <t>65216; 95923</t>
         </is>
       </c>
     </row>
